--- a/data/trans_dic/IP07_C14_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C14_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 20,54</t>
+          <t>5,62; 23,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 23,81</t>
+          <t>3,38; 19,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 19,52</t>
+          <t>6,08; 18,76</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 23,08</t>
+          <t>5,14; 16,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 19,08</t>
+          <t>6,5; 20,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 17,72</t>
+          <t>6,73; 16,43</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 20,6</t>
+          <t>2,53; 16,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 16,79</t>
+          <t>8,59; 26,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 16,23</t>
+          <t>7,19; 18,44</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,76; 32,28</t>
+          <t>13,56; 35,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,59; 37,26</t>
+          <t>11,6; 31,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,01; 30,18</t>
+          <t>15,01; 28,83</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 18,09</t>
+          <t>8,94; 17,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,41</t>
+          <t>11,18; 19,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,03; 16,33</t>
+          <t>10,57; 16,58</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>9147</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1067; 6402</t>
+          <t>2634; 10890</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2175; 11276</t>
+          <t>1155; 6503</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4557; 15328</t>
+          <t>4927; 15204</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>16835</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3851; 12101</t>
+          <t>5180; 16911</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5976; 19374</t>
+          <t>3640; 11431</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11532; 27282</t>
+          <t>10555; 25756</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>7473</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11640</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1701; 14485</t>
+          <t>1316; 8681</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1438; 8804</t>
+          <t>4067; 12522</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5167; 19923</t>
+          <t>7144; 18327</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>21261</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5646; 15492</t>
+          <t>6703; 17781</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6735; 18468</t>
+          <t>5910; 15981</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14646; 29441</t>
+          <t>15063; 28935</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>31593</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>58883</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16535; 36535</t>
+          <t>22255; 42528</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24269; 46183</t>
+          <t>21073; 36454</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45397; 73927</t>
+          <t>46261; 72535</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP07_C14_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C14_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores en cuyo colegio/instituto se han producido situaciones de cyberbulling (tasa de respuesta: 94,11%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12,92%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5,62; 23,23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3,38; 19,02</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,08; 18,76</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12,66%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>5,14; 16,79</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6,5; 20,41</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6,73; 16,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2,53; 16,69</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8,59; 26,44</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7,19; 18,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>21,18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>13,56; 35,98</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11,6; 31,36</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15,01; 28,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>8,94; 17,07</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11,18; 19,34</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10,57; 16,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1292159671588513</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.09037958241636049</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.112841144883583</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6058</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3089</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9147</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.05618882288202982</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.03379911633083159</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.060777127827633</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2634; 10890</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1155; 6503</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4927; 15204</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.2322685576242204</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1902447238223626</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1875549072720342</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.09670514449628269</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.126628118976022</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1073980001265632</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>9742</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7093</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16835</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.05142002863996482</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.06498233242411151</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.0673316627525055</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5180; 16911</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3640; 11431</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10555; 25756</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.167871879865752</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2040731527570896</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1643091170815982</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.08009007592793556</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.157802648462814</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1171221838299063</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4167</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7473</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11640</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.02529541042405953</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.08587335794528329</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.07188417665565386</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1316; 8681</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4067; 12522</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7144; 18327</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1668651082323681</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.264417315831608</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1844086743338292</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.2352461048885907</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1890851934618567</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2118124666445678</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>11626</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9635</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21261</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1356370549388353</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1159732882888075</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1500671603366591</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>6703; 17781</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>5910; 15981</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15063; 28935</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.3598036838801851</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.3136174986631651</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2882616346960017</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.126844091474199</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1447701304171976</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.134566677027244</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>31593</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>27291</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>58883</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.08935487176589624</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1117886073694327</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1057216195365285</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>22255; 42528</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>21073; 36454</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>46261; 72535</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1707497838914276</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.193378280641898</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1657644140181148</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores en cuyo colegio/instituto se han producido situaciones de cyberbulling (tasa de respuesta: 94,11%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>6058</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3089</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>9147</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2634</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1155</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>4927</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>10890</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>6503</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>15204</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>9742</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>7093</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>16835</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>5180</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3640</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>10555</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>16911</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>11431</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>25756</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4167</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>7473</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>11640</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1316</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>4067</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>7144</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>8681</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>12522</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>18327</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>11626</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9635</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>21261</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>6703</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>5910</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>15063</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>17781</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>15981</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>28935</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>31593</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>27291</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>58883</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>22255</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>21073</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>42528</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>36454</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>72535</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>